--- a/BDCI.xlsx
+++ b/BDCI.xlsx
@@ -158,7 +158,43 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -169,6 +205,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tableau1" displayName="Tableau1" ref="A1:G44" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:G44"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="تاريخ" dataDxfId="6"/>
+    <tableColumn id="2" name="المنتوجات"/>
+    <tableColumn id="3" name="سعر تفصيل" dataDxfId="5"/>
+    <tableColumn id="4" name="سعر أدنى جملة" dataDxfId="4"/>
+    <tableColumn id="5" name="سعر أقصى جملة" dataDxfId="3"/>
+    <tableColumn id="6" name="سعر أدنى تفصيل" dataDxfId="2"/>
+    <tableColumn id="7" name="سعر أقصى تفصيل" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,11 +491,11 @@
   <cols>
     <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1461,5 +1513,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>